--- a/backup/17-07-26.xlsx
+++ b/backup/17-07-26.xlsx
@@ -73,7 +73,7 @@
     <t xml:space="preserve">Prática Clínica - Preenchimento Facial</t>
   </si>
   <si>
-    <t xml:space="preserve">Paulista</t>
+    <t xml:space="preserve">São Paulo</t>
   </si>
   <si>
     <t xml:space="preserve">Prática Clinica        </t>
